--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N90_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N90_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>35.81140391080353</v>
+        <v>5.819353135505574</v>
       </c>
       <c r="D2" t="n">
-        <v>35.14463763252196</v>
+        <v>5.711003615284818</v>
       </c>
       <c r="E2" t="n">
-        <v>8.583994588190711</v>
+        <v>1.394899120580991</v>
       </c>
       <c r="F2" t="n">
-        <v>12.40271424467023</v>
+        <v>2.015441064758912</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>36.24095115325198</v>
+        <v>5.889154562403448</v>
       </c>
       <c r="D3" t="n">
-        <v>37.47246929465692</v>
+        <v>6.089276260381749</v>
       </c>
       <c r="E3" t="n">
-        <v>8.583994588190711</v>
+        <v>1.394899120580991</v>
       </c>
       <c r="F3" t="n">
-        <v>12.40271424467023</v>
+        <v>2.015441064758912</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>38.08747731155785</v>
+        <v>6.189215063128152</v>
       </c>
       <c r="D4" t="n">
-        <v>39.09573566448164</v>
+        <v>6.353057045478267</v>
       </c>
       <c r="E4" t="n">
-        <v>8.583994588190711</v>
+        <v>1.394899120580991</v>
       </c>
       <c r="F4" t="n">
-        <v>12.40271424467023</v>
+        <v>2.015441064758912</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>50.26875122736615</v>
+        <v>8.168672074447</v>
       </c>
       <c r="D5" t="n">
-        <v>51.23240304763662</v>
+        <v>8.325265495240952</v>
       </c>
       <c r="E5" t="n">
-        <v>8.583994588190711</v>
+        <v>1.394899120580991</v>
       </c>
       <c r="F5" t="n">
-        <v>12.40271424467023</v>
+        <v>2.015441064758912</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>37.03526077522277</v>
+        <v>6.018229875973701</v>
       </c>
       <c r="D6" t="n">
-        <v>7.566372975210778</v>
+        <v>1.229535608471751</v>
       </c>
       <c r="E6" t="n">
-        <v>8.583994588190711</v>
+        <v>1.394899120580991</v>
       </c>
       <c r="F6" t="n">
-        <v>12.40271424467023</v>
+        <v>2.015441064758912</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>23.29496004593332</v>
+        <v>3.785431007464165</v>
       </c>
       <c r="D7" t="n">
-        <v>23.85244622234514</v>
+        <v>3.876022511131086</v>
       </c>
       <c r="E7" t="n">
-        <v>8.583994588190711</v>
+        <v>1.394899120580991</v>
       </c>
       <c r="F7" t="n">
-        <v>12.40271424467023</v>
+        <v>2.015441064758912</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>21.05988912682203</v>
+        <v>3.42223198310858</v>
       </c>
       <c r="D8" t="n">
-        <v>21.16514680213393</v>
+        <v>3.439336355346764</v>
       </c>
       <c r="E8" t="n">
-        <v>8.583994588190711</v>
+        <v>1.394899120580991</v>
       </c>
       <c r="F8" t="n">
-        <v>12.40271424467023</v>
+        <v>2.015441064758912</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>31.06191485774027</v>
+        <v>5.047561164382794</v>
       </c>
       <c r="D9" t="n">
-        <v>30.93689333852228</v>
+        <v>5.027245167509871</v>
       </c>
       <c r="E9" t="n">
-        <v>8.583994588190711</v>
+        <v>1.394899120580991</v>
       </c>
       <c r="F9" t="n">
-        <v>12.40271424467023</v>
+        <v>2.015441064758912</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
